--- a/research/traditional_assets/database/data/mozambique/mozambique_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/mozambique/mozambique_farming_agriculture.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.03602941176470588</v>
+        <v>-0.0009615384615384615</v>
       </c>
       <c r="H2">
-        <v>-0.03602941176470588</v>
+        <v>-0.0009615384615384615</v>
       </c>
       <c r="I2">
-        <v>-0.07794117647058824</v>
+        <v>-0.07586538461538461</v>
       </c>
       <c r="J2">
-        <v>-0.07794117647058824</v>
+        <v>-0.07586538461538461</v>
       </c>
       <c r="K2">
-        <v>-2.38</v>
+        <v>-2.44</v>
       </c>
       <c r="L2">
-        <v>-0.175</v>
+        <v>-0.2346153846153846</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.283</v>
+        <v>0.35</v>
       </c>
       <c r="V2">
-        <v>0.1791139240506329</v>
+        <v>0.3937007874015748</v>
       </c>
       <c r="W2">
-        <v>-24.28571428571428</v>
+        <v>-0.1936507936507937</v>
       </c>
       <c r="X2">
-        <v>0.5832319153782045</v>
+        <v>1.410150517824338</v>
       </c>
       <c r="Y2">
-        <v>-24.86894620109249</v>
+        <v>-1.603801311475131</v>
       </c>
       <c r="Z2">
-        <v>1.986271359719585</v>
+        <v>0.4460265042672728</v>
       </c>
       <c r="AA2">
-        <v>-0.1548123265663794</v>
+        <v>-0.03383797229489214</v>
       </c>
       <c r="AB2">
-        <v>0.1372410782674407</v>
+        <v>0.2093596650369042</v>
       </c>
       <c r="AC2">
-        <v>-0.2920534048338201</v>
+        <v>-0.2431976373317964</v>
       </c>
       <c r="AD2">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="AG2">
-        <v>10.717</v>
+        <v>10.95</v>
       </c>
       <c r="AH2">
-        <v>0.8744038155802861</v>
+        <v>0.9270653868241858</v>
       </c>
       <c r="AI2">
-        <v>0.4661016949152542</v>
+        <v>0.5345316934720908</v>
       </c>
       <c r="AJ2">
-        <v>0.8715133772464829</v>
+        <v>0.9249091984120281</v>
       </c>
       <c r="AK2">
-        <v>0.4596217352146503</v>
+        <v>0.5266955266955268</v>
       </c>
       <c r="AL2">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="AM2">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="AN2">
-        <v>-35.14376996805112</v>
+        <v>217.3076923076923</v>
       </c>
       <c r="AO2">
-        <v>-0.7681159420289856</v>
+        <v>-0.4311475409836066</v>
       </c>
       <c r="AP2">
-        <v>-34.23961661341853</v>
+        <v>210.5769230769231</v>
       </c>
       <c r="AQ2">
-        <v>-0.7681159420289856</v>
+        <v>-0.4311475409836066</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.03602941176470588</v>
+        <v>-0.0009615384615384615</v>
       </c>
       <c r="H3">
-        <v>-0.03602941176470588</v>
+        <v>-0.0009615384615384615</v>
       </c>
       <c r="I3">
-        <v>-0.07794117647058824</v>
+        <v>-0.07586538461538461</v>
       </c>
       <c r="J3">
-        <v>-0.07794117647058824</v>
+        <v>-0.07586538461538461</v>
       </c>
       <c r="K3">
-        <v>-2.38</v>
+        <v>-2.44</v>
       </c>
       <c r="L3">
-        <v>-0.175</v>
+        <v>-0.2346153846153846</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.283</v>
+        <v>0.35</v>
       </c>
       <c r="V3">
-        <v>0.1791139240506329</v>
+        <v>0.3937007874015748</v>
       </c>
       <c r="W3">
-        <v>-24.28571428571428</v>
+        <v>-0.1936507936507937</v>
       </c>
       <c r="X3">
-        <v>0.5832319153782045</v>
+        <v>1.410150517824338</v>
       </c>
       <c r="Y3">
-        <v>-24.86894620109249</v>
+        <v>-1.603801311475131</v>
       </c>
       <c r="Z3">
-        <v>1.986271359719585</v>
+        <v>0.4460265042672728</v>
       </c>
       <c r="AA3">
-        <v>-0.1548123265663794</v>
+        <v>-0.03383797229489214</v>
       </c>
       <c r="AB3">
-        <v>0.1372410782674407</v>
+        <v>0.2093596650369042</v>
       </c>
       <c r="AC3">
-        <v>-0.2920534048338201</v>
+        <v>-0.2431976373317964</v>
       </c>
       <c r="AD3">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="AG3">
-        <v>10.717</v>
+        <v>10.95</v>
       </c>
       <c r="AH3">
-        <v>0.8744038155802861</v>
+        <v>0.9270653868241858</v>
       </c>
       <c r="AI3">
-        <v>0.4661016949152542</v>
+        <v>0.5345316934720908</v>
       </c>
       <c r="AJ3">
-        <v>0.8715133772464829</v>
+        <v>0.9249091984120281</v>
       </c>
       <c r="AK3">
-        <v>0.4596217352146503</v>
+        <v>0.5266955266955268</v>
       </c>
       <c r="AL3">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="AM3">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="AN3">
-        <v>-35.14376996805112</v>
+        <v>217.3076923076923</v>
       </c>
       <c r="AO3">
-        <v>-0.7681159420289856</v>
+        <v>-0.4311475409836066</v>
       </c>
       <c r="AP3">
-        <v>-34.23961661341853</v>
+        <v>210.5769230769231</v>
       </c>
       <c r="AQ3">
-        <v>-0.7681159420289856</v>
+        <v>-0.4311475409836066</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/mozambique/mozambique_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/mozambique/mozambique_farming_agriculture.xlsx
@@ -587,23 +587,26 @@
           <t>Farming/Agriculture</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.0108</v>
+      </c>
       <c r="G2">
-        <v>-0.0009615384615384615</v>
+        <v>0.004257425742574257</v>
       </c>
       <c r="H2">
-        <v>-0.0009615384615384615</v>
+        <v>0.004257425742574257</v>
       </c>
       <c r="I2">
-        <v>-0.07586538461538461</v>
+        <v>-0.1396039603960396</v>
       </c>
       <c r="J2">
-        <v>-0.07586538461538461</v>
+        <v>-0.1396039603960396</v>
       </c>
       <c r="K2">
-        <v>-2.44</v>
+        <v>-2.36</v>
       </c>
       <c r="L2">
-        <v>-0.2346153846153846</v>
+        <v>-0.2336633663366336</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.35</v>
+        <v>0.307</v>
       </c>
       <c r="V2">
-        <v>0.3937007874015748</v>
+        <v>0.4475218658892128</v>
       </c>
       <c r="W2">
-        <v>-0.1936507936507937</v>
+        <v>-0.2398373983739837</v>
       </c>
       <c r="X2">
-        <v>1.410150517824338</v>
+        <v>1.491253706503522</v>
       </c>
       <c r="Y2">
-        <v>-1.603801311475131</v>
+        <v>-1.731091104877506</v>
       </c>
       <c r="Z2">
-        <v>0.4460265042672728</v>
+        <v>0.4858104858104858</v>
       </c>
       <c r="AA2">
-        <v>-0.03383797229489214</v>
+        <v>-0.06782106782106782</v>
       </c>
       <c r="AB2">
-        <v>0.2093596650369042</v>
+        <v>0.172672733009569</v>
       </c>
       <c r="AC2">
-        <v>-0.2431976373317964</v>
+        <v>-0.2404938008306369</v>
       </c>
       <c r="AD2">
-        <v>11.3</v>
+        <v>13</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>11.3</v>
+        <v>13</v>
       </c>
       <c r="AG2">
-        <v>10.95</v>
+        <v>12.693</v>
       </c>
       <c r="AH2">
-        <v>0.9270653868241858</v>
+        <v>0.9498757854742073</v>
       </c>
       <c r="AI2">
-        <v>0.5345316934720908</v>
+        <v>0.6280193236714976</v>
       </c>
       <c r="AJ2">
-        <v>0.9249091984120281</v>
+        <v>0.9487256147694147</v>
       </c>
       <c r="AK2">
-        <v>0.5266955266955268</v>
+        <v>0.6224194576570391</v>
       </c>
       <c r="AL2">
-        <v>1.83</v>
+        <v>1.09</v>
       </c>
       <c r="AM2">
-        <v>1.83</v>
+        <v>1.09</v>
       </c>
       <c r="AN2">
-        <v>217.3076923076923</v>
+        <v>-21.92242833052277</v>
       </c>
       <c r="AO2">
-        <v>-0.4311475409836066</v>
+        <v>-1.293577981651376</v>
       </c>
       <c r="AP2">
-        <v>210.5769230769231</v>
+        <v>-21.40472175379427</v>
       </c>
       <c r="AQ2">
-        <v>-0.4311475409836066</v>
+        <v>-1.293577981651376</v>
       </c>
     </row>
     <row r="3">
@@ -712,23 +715,26 @@
           <t>Farming/Agriculture</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.0108</v>
+      </c>
       <c r="G3">
-        <v>-0.0009615384615384615</v>
+        <v>0.004257425742574257</v>
       </c>
       <c r="H3">
-        <v>-0.0009615384615384615</v>
+        <v>0.004257425742574257</v>
       </c>
       <c r="I3">
-        <v>-0.07586538461538461</v>
+        <v>-0.1396039603960396</v>
       </c>
       <c r="J3">
-        <v>-0.07586538461538461</v>
+        <v>-0.1396039603960396</v>
       </c>
       <c r="K3">
-        <v>-2.44</v>
+        <v>-2.36</v>
       </c>
       <c r="L3">
-        <v>-0.2346153846153846</v>
+        <v>-0.2336633663366336</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.35</v>
+        <v>0.307</v>
       </c>
       <c r="V3">
-        <v>0.3937007874015748</v>
+        <v>0.4475218658892128</v>
       </c>
       <c r="W3">
-        <v>-0.1936507936507937</v>
+        <v>-0.2398373983739837</v>
       </c>
       <c r="X3">
-        <v>1.410150517824338</v>
+        <v>1.491253706503522</v>
       </c>
       <c r="Y3">
-        <v>-1.603801311475131</v>
+        <v>-1.731091104877506</v>
       </c>
       <c r="Z3">
-        <v>0.4460265042672728</v>
+        <v>0.4858104858104858</v>
       </c>
       <c r="AA3">
-        <v>-0.03383797229489214</v>
+        <v>-0.06782106782106782</v>
       </c>
       <c r="AB3">
-        <v>0.2093596650369042</v>
+        <v>0.172672733009569</v>
       </c>
       <c r="AC3">
-        <v>-0.2431976373317964</v>
+        <v>-0.2404938008306369</v>
       </c>
       <c r="AD3">
-        <v>11.3</v>
+        <v>13</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>11.3</v>
+        <v>13</v>
       </c>
       <c r="AG3">
-        <v>10.95</v>
+        <v>12.693</v>
       </c>
       <c r="AH3">
-        <v>0.9270653868241858</v>
+        <v>0.9498757854742073</v>
       </c>
       <c r="AI3">
-        <v>0.5345316934720908</v>
+        <v>0.6280193236714976</v>
       </c>
       <c r="AJ3">
-        <v>0.9249091984120281</v>
+        <v>0.9487256147694147</v>
       </c>
       <c r="AK3">
-        <v>0.5266955266955268</v>
+        <v>0.6224194576570391</v>
       </c>
       <c r="AL3">
-        <v>1.83</v>
+        <v>1.09</v>
       </c>
       <c r="AM3">
-        <v>1.83</v>
+        <v>1.09</v>
       </c>
       <c r="AN3">
-        <v>217.3076923076923</v>
+        <v>-21.92242833052277</v>
       </c>
       <c r="AO3">
-        <v>-0.4311475409836066</v>
+        <v>-1.293577981651376</v>
       </c>
       <c r="AP3">
-        <v>210.5769230769231</v>
+        <v>-21.40472175379427</v>
       </c>
       <c r="AQ3">
-        <v>-0.4311475409836066</v>
+        <v>-1.293577981651376</v>
       </c>
     </row>
   </sheetData>
